--- a/03_Test_Cases/Test_Cases.xlsx
+++ b/03_Test_Cases/Test_Cases.xlsx
@@ -1,29 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationExercise_Automation_Project_Templates\03_Test_Cases\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6C12FD-F0EB-4B1B-8559-5C13AC53D99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="Registration" sheetId="2" r:id="rId2"/>
     <sheet name="Cart" sheetId="3" r:id="rId3"/>
     <sheet name="Checkout" sheetId="4" r:id="rId4"/>
+    <sheet name="Navigatoion" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="116">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -281,13 +276,103 @@
   </si>
   <si>
     <t>Checkout cancelled</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>TC021</t>
+  </si>
+  <si>
+    <t>TC022</t>
+  </si>
+  <si>
+    <t>TC023</t>
+  </si>
+  <si>
+    <t>TC024</t>
+  </si>
+  <si>
+    <t>TC025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Products Page Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Click Products menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Cart Page Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Login Page Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Category Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Add to Cart Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Click Cart menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Click Signup/Login menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Click Women → Dress category</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add product → Open cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User navigates to Products page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User navigates to Cart page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User navigates to Login page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Women products should display</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product visible in cart</t>
+  </si>
+  <si>
+    <t>Navigated to products page</t>
+  </si>
+  <si>
+    <t>Navigated to cart page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Navigated to login page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Category element not found</t>
+  </si>
+  <si>
+    <t>Executed</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,18 +704,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -653,7 +738,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -673,7 +758,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -693,7 +778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -713,7 +798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -733,7 +818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -759,20 +844,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -795,7 +880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -815,7 +900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -835,7 +920,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -855,7 +940,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -875,7 +960,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -901,20 +986,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -937,7 +1022,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -957,7 +1042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -977,7 +1062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -997,7 +1082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -1017,7 +1102,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -1043,20 +1128,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1079,7 +1164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1099,7 +1184,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1119,7 +1204,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1139,7 +1224,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -1159,7 +1244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1177,9 +1262,209 @@
       </c>
       <c r="G6" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="10:10">
+      <c r="J23" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" customWidth="1"/>
+    <col min="6" max="6" width="25.21875" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="J12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/03_Test_Cases/Test_Cases.xlsx
+++ b/03_Test_Cases/Test_Cases.xlsx
@@ -365,7 +365,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t xml:space="preserve"> Pass </t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1446,7 +1446,7 @@
         <v>112</v>
       </c>
       <c r="H6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:10">

--- a/03_Test_Cases/Test_Cases.xlsx
+++ b/03_Test_Cases/Test_Cases.xlsx
@@ -1,24 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ecommerce Testing\AutomationExcercise\03_Test_Cases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D52083-3B5E-4B67-8C95-65D59FAF8071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" activeTab="4"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="Registration" sheetId="2" r:id="rId2"/>
-    <sheet name="Cart" sheetId="3" r:id="rId3"/>
+    <sheet name="Products" sheetId="3" r:id="rId3"/>
     <sheet name="Checkout" sheetId="4" r:id="rId4"/>
     <sheet name="Navigatoion" sheetId="5" r:id="rId5"/>
+    <sheet name="TestRun_Sheet" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="174">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -158,222 +165,855 @@
     <t>Success message displayed</t>
   </si>
   <si>
-    <t>TC011</t>
-  </si>
-  <si>
-    <t>Add product to cart</t>
+    <t>Remove product from cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>TC021</t>
+  </si>
+  <si>
+    <t>TC022</t>
+  </si>
+  <si>
+    <t>TC023</t>
+  </si>
+  <si>
+    <t>TC024</t>
+  </si>
+  <si>
+    <t>TC025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Products Page Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Click Products menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Cart Page Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Login Page Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Category Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify Add to Cart Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Click Cart menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Click Signup/Login menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Click Women → Dress category</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add product → Open cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User navigates to Products page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User navigates to Cart page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User navigates to Login page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Women products should display</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product visible in cart</t>
+  </si>
+  <si>
+    <t>Navigated to products page</t>
+  </si>
+  <si>
+    <t>Navigated to cart page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Navigated to login page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Category element not found</t>
+  </si>
+  <si>
+    <t>Executed</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pass </t>
+  </si>
+  <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>CHK_001</t>
+  </si>
+  <si>
+    <t>Checkout after login</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>CHK_002</t>
+  </si>
+  <si>
+    <t>Checkout without login</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>CHK_003</t>
+  </si>
+  <si>
+    <t>Payment with valid card</t>
+  </si>
+  <si>
+    <t>CHK_004</t>
+  </si>
+  <si>
+    <t>Verify address detail visible</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>PROD_001</t>
+  </si>
+  <si>
+    <t>Search product valid keyword</t>
+  </si>
+  <si>
+    <t>PROD_002</t>
+  </si>
+  <si>
+    <t>Search product invalid keyword</t>
+  </si>
+  <si>
+    <t>PROD_003</t>
+  </si>
+  <si>
+    <t>Add multiple products to cart</t>
+  </si>
+  <si>
+    <t>PROD_004</t>
+  </si>
+  <si>
+    <t>PROD_005</t>
+  </si>
+  <si>
+    <t>Add product from details page with qty</t>
+  </si>
+  <si>
+    <t>PROD_006</t>
+  </si>
+  <si>
+    <t>Verify cart persist after refresh</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Valid user account exists (credentials stored in config/properties).</t>
+  </si>
+  <si>
+    <t>User is NOT logged in.</t>
+  </si>
+  <si>
+    <t>Valid user account exists and user profile has an address saved.</t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>1. Open AutomationExercise website
+2. Click Signup / Login
+3. Enter valid email &amp; password and login
+4. Click Products
+5. Add any product to cart
+6. Click Cart
+7. Click Proceed To Checkout</t>
+  </si>
+  <si>
+    <t>1. Open AutomationExercise website
+2. Click Products
+3. Add any product to cart
+4. Click Cart
+5. Click Proceed To Checkout</t>
+  </si>
+  <si>
+    <t>1. Open AutomationExercise website
+2. Login with valid credentials
+3. Click Products
+4. Add any product to cart
+5. Click Cart
+6. Click Proceed To Checkout
+7. Click Place Order
+8. Fill payment details
+9. Click Pay and Confirm Order</t>
+  </si>
+  <si>
+    <t>1. Open AutomationExercise website
+2. Login with valid credentials
+3. Click Products
+4. Add any product to cart
+5. Click Cart
+6. Click Proceed To Checkout
+7. Verify Delivery Address section is displayed
+8. Verify Billing Address section is displayed</t>
+  </si>
+  <si>
+    <t>User should navigate to Checkout page (URL contains /checkout) and checkout page should load.</t>
+  </si>
+  <si>
+    <t>A modal/popup should appear with message containing 'Register / Login' and Register/Login button should be visible.</t>
+  </si>
+  <si>
+    <t>Order should be placed successfully and 'ORDER PLACED!' (or success message) should be displayed.</t>
+  </si>
+  <si>
+    <t>Delivery Address and Billing Address blocks should be visible on checkout page.</t>
+  </si>
+  <si>
+    <t>Expected_Result</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Run</t>
+  </si>
+  <si>
+    <t>User is on AutomationExercise website</t>
+  </si>
+  <si>
+    <t>At least 1 product is already added to cart,User is on Cart page</t>
+  </si>
+  <si>
+    <t>User is on AutomationExercise website,Products page is accessible and Cart is empty (recommended).</t>
+  </si>
+  <si>
+    <t>At least 1 product added to cart and User is on Cart page.</t>
+  </si>
+  <si>
+    <t>Open application-&gt;Navigate to Products-&gt;Click on any product View Product-&gt;Increase quantity (example: set to 2)-&gt;Click Add to cart-&gt;Click View Cart-&gt;Verify quantity and product in cart</t>
+  </si>
+  <si>
+    <t>Open application-&gt;Navigate to Products page-&gt;Enter a valid Keyword(example: Dress) in search box-&gt;Click Search-&gt;Verify search result displayed</t>
+  </si>
+  <si>
+    <t>Open application-&gt;Navigate to Products page-&gt;Enter a Invalid Keyword(example: xyz1235) in search box-&gt;Click Search-&gt;Observe the result section</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open application -&gt; Navigate to Products page -&gt; Add product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Blue Top"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to cart -&gt; Continue Shopping -&gt; Add product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Men Tshirt"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to cart -&gt; Continue Shopping -&gt; Add product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Sleeveless Dress"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to cart -&gt; Click Cart</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open application -&gt; Navigate to Products page -&gt; Add product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Blue Top"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to cart -&gt; Continue Shopping -&gt; Add product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Men Tshirt"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to cart -&gt; Continue Shopping -&gt; Add product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Sleeveless Dress"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to cart -&gt; Click Cart -&gt; Remove product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Men Tshirt"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; Remove product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Sleeveless Dress"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open application -&gt; Navigate to Products page -&gt; Add product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Blue Top"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to cart -&gt; Continue Shopping -&gt; Add product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Men Tshirt"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to cart -&gt; Continue Shopping -&gt; Add product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Sleeveless Dress"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to cart -&gt; Click Cart -&gt; Refresh the page</t>
+    </r>
+  </si>
+  <si>
+    <t>Expected Rresult</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">User should see </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Searched Products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> heading and at least </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> related to keyword “Dress” displayed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">User should see </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Searched Products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> heading and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0 products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> displayed for invalid keyword.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cart should contain </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3 products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Blue Top,Mens Tshirt,Sleeveless Dress</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cart should display product </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Blue Top</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with quantity </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Only </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should remain in cart: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Blue Top</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>After refresh:Cart should still contain 3 products,Products should remain unchanged (Blue Top, Men Tshirt, Sleeveless Dress)</t>
+  </si>
+  <si>
+    <t>Run_ID</t>
+  </si>
+  <si>
+    <t>Execution Date</t>
+  </si>
+  <si>
+    <t>Executed By</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Defect ID</t>
+  </si>
+  <si>
+    <t>RUN_001</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Searched Products heading should be visible and at least 1 product should be displayed for keyword "Dress".</t>
+  </si>
+  <si>
+    <t>Searched Products heading should be visible and 0 products should be displayed for keyword "xyz1235".</t>
+  </si>
+  <si>
+    <t>Cart should contain 3 products: Blue Top, Men Tshirt, Sleeveless Dress.</t>
+  </si>
+  <si>
+    <t>After removing Men Tshirt and Sleeveless Dress, only Blue Top should remain in cart.</t>
+  </si>
+  <si>
+    <t>Product Details</t>
+  </si>
+  <si>
+    <t>Cart should display product Blue Top with quantity 4.</t>
   </si>
   <si>
     <t>Cart</t>
   </si>
   <si>
-    <t>Click Add to cart button</t>
-  </si>
-  <si>
-    <t>Product added successfully</t>
-  </si>
-  <si>
-    <t>TC012</t>
-  </si>
-  <si>
-    <t>Add multiple products</t>
-  </si>
-  <si>
-    <t>Add more than one product</t>
-  </si>
-  <si>
-    <t>All products added</t>
-  </si>
-  <si>
-    <t>TC013</t>
-  </si>
-  <si>
-    <t>Remove product from cart</t>
-  </si>
-  <si>
-    <t>Click remove button</t>
-  </si>
-  <si>
-    <t>Product removed successfully</t>
-  </si>
-  <si>
-    <t>TC014</t>
-  </si>
-  <si>
-    <t>Verify cart total</t>
-  </si>
-  <si>
-    <t>Add product and check total</t>
-  </si>
-  <si>
-    <t>Total calculated correctly</t>
-  </si>
-  <si>
-    <t>TC015</t>
-  </si>
-  <si>
-    <t>Add product without login</t>
-  </si>
-  <si>
-    <t>Product added or login prompted</t>
-  </si>
-  <si>
-    <t>TC016</t>
-  </si>
-  <si>
-    <t>Checkout with valid data</t>
+    <t>After refresh, cart should still contain 3 products and products should remain unchanged.</t>
+  </si>
+  <si>
+    <t>Search results displayed for valid keyword.</t>
+  </si>
+  <si>
+    <t>No products displayed for invalid keyword.</t>
+  </si>
+  <si>
+    <t>3 products successfully added to cart.</t>
+  </si>
+  <si>
+    <t>Selected products removed; 1 product remained.</t>
+  </si>
+  <si>
+    <t>Product added with correct quantity.</t>
+  </si>
+  <si>
+    <t>Cart data remained after refresh.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>BUG_001</t>
+  </si>
+  <si>
+    <t>Subrat Gupta</t>
+  </si>
+  <si>
+    <t>RUN_002</t>
+  </si>
+  <si>
+    <t>Refer TestNG Report</t>
+  </si>
+  <si>
+    <t>Checkout has done successfully with valid login.</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>BUG_002</t>
   </si>
   <si>
     <t>Checkout</t>
   </si>
   <si>
-    <t>Add product and checkout</t>
-  </si>
-  <si>
-    <t>Checkout successful</t>
-  </si>
-  <si>
-    <t>TC017</t>
-  </si>
-  <si>
-    <t>Checkout with empty cart</t>
-  </si>
-  <si>
-    <t>Click checkout with empty cart</t>
-  </si>
-  <si>
-    <t>TC018</t>
-  </si>
-  <si>
-    <t>Verify payment page</t>
-  </si>
-  <si>
-    <t>Proceed to checkout</t>
-  </si>
-  <si>
-    <t>Payment page displayed</t>
-  </si>
-  <si>
-    <t>TC019</t>
-  </si>
-  <si>
-    <t>Verify order confirmation</t>
-  </si>
-  <si>
-    <t>Complete payment</t>
-  </si>
-  <si>
-    <t>Order confirmed</t>
-  </si>
-  <si>
-    <t>TC020</t>
-  </si>
-  <si>
-    <t>Cancel checkout</t>
-  </si>
-  <si>
-    <t>Cancel checkout process</t>
-  </si>
-  <si>
-    <t>Checkout cancelled</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>TC021</t>
-  </si>
-  <si>
-    <t>TC022</t>
-  </si>
-  <si>
-    <t>TC023</t>
-  </si>
-  <si>
-    <t>TC024</t>
-  </si>
-  <si>
-    <t>TC025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Verify Products Page Navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Click Products menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Verify Cart Page Navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Verify Login Page Navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Verify Category Navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Verify Add to Cart Flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Click Cart menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Click Signup/Login menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Click Women → Dress category</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Add product → Open cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> User navigates to Products page</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> User navigates to Cart page</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> User navigates to Login page</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Women products should display</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Product visible in cart</t>
-  </si>
-  <si>
-    <t>Navigated to products page</t>
-  </si>
-  <si>
-    <t>Navigated to cart page</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Navigated to login page</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Category element not found</t>
-  </si>
-  <si>
-    <t>Executed</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pass </t>
+    <t>Modal has appeared with Register/Login button.</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>Order placed Successfully with mesaage 'ORDER PLACED!'</t>
+  </si>
+  <si>
+    <t>Delivery Address and Billing Address blocks are visible.</t>
+  </si>
+  <si>
+    <t>BUG_006</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -401,8 +1041,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,9 +1084,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -461,7 +1124,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -495,6 +1158,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -529,9 +1193,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -704,9 +1369,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.21875" bestFit="1" customWidth="1"/>
@@ -715,7 +1380,7 @@
     <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -738,7 +1403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -758,7 +1423,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -778,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -798,7 +1463,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -818,7 +1483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -844,9 +1509,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
@@ -857,7 +1522,7 @@
     <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -880,7 +1545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -900,7 +1565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -920,7 +1585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -940,7 +1605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -960,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -986,141 +1651,211 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.33203125" customWidth="1"/>
+    <col min="4" max="5" width="72.44140625" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" customWidth="1"/>
+    <col min="7" max="7" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
+      <c r="C5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E10" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1128,150 +1863,159 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.21875" customWidth="1"/>
+    <col min="4" max="5" width="29.21875" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
+    <row r="2" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="B2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="G2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H2" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="B3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="10:10">
-      <c r="J23" t="s">
-        <v>86</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M23" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1280,9 +2024,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
@@ -1293,7 +2037,7 @@
     <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1316,155 +2060,566 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J12" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450C9D24-32BA-4D2E-9C96-300EE921997B}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" customWidth="1"/>
+    <col min="7" max="7" width="22.109375" customWidth="1"/>
+    <col min="8" max="8" width="25.77734375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="37.88671875" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J4" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" t="s">
+        <v>163</v>
+      </c>
+      <c r="K5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J6" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" t="s">
+        <v>163</v>
+      </c>
+      <c r="K8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E10" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{8DD3C86D-806C-4DD5-86D7-AFF565DF1F71}">
+      <formula1>"Pass,Fail,Blocked,Not Executed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/03_Test_Cases/Test_Cases.xlsx
+++ b/03_Test_Cases/Test_Cases.xlsx
@@ -1417,10 +1417,10 @@
         <v>111</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:10">
